--- a/_data/PLCTags_FG03.xlsx
+++ b/_data/PLCTags_FG03.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC Tags" sheetId="1" r:id="R7b5c2c3dd8744901"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="R6f5844b6f2de4049"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC Tags" sheetId="1" r:id="R1fe571f9865b475e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="Ra83ccbca45fa45b2"/>
   </x:sheets>
 </x:workbook>
 </file>
